--- a/outputs/02_Competitor_Website_Audit.xlsx
+++ b/outputs/02_Competitor_Website_Audit.xlsx
@@ -505,7 +505,7 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Companion files: 01_Peptide_Market_Landscape.csv, 03_Peptide_Product_and_Pricing_Audit.xlsx, 08_AminoLord_Evidence_Ledger.xlsx (all source URLs).</t>
+          <t>Companion files: 01_Peptide_Market_Landscape.csv, 03_Peptide_Product_and_Pricing_Audit.xlsx, 08_ReserveClinic_Evidence_Ledger.xlsx (all source URLs).</t>
         </is>
       </c>
     </row>
